--- a/Rodovias/modelos_rodovias/floriano_rodrigues_pinheiro_km_26_pindamonhangaba_sp_rf_regimes/importancias.xlsx
+++ b/Rodovias/modelos_rodovias/floriano_rodrigues_pinheiro_km_26_pindamonhangaba_sp_rf_regimes/importancias.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B83"/>
+  <dimension ref="A1:B38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -435,817 +435,367 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.04030853242878672</v>
+        <v>0.09180322963693868</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>meta_num</t>
+          <t>interacao_meta_hora_sin</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.03843933809732696</v>
+        <v>0.08775957850539987</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>interacao_meta_temperatura</t>
+          <t>interacao_meta_hora_cos</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.03342358930948758</v>
+        <v>0.0857921647217891</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>interacao_meta_hora_sin</t>
+          <t>interacao_meta_temperatura</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.02932894879165944</v>
+        <v>0.08570012242804775</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>minuto</t>
+          <t>meta_num</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.0279162175859079</v>
+        <v>0.08320753511633729</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>interacao_meta_hora_cos</t>
+          <t>minuto</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.02759217241416366</v>
+        <v>0.08039249665179352</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>meta_delta_media_12</t>
+          <t>hora_cos</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.02676593046295246</v>
+        <v>0.07527899155719341</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>tendencia_curta_meta</t>
+          <t>hora_decimal</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.02595427466135536</v>
+        <v>0.07076280821991568</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>meta_delta_media_4</t>
+          <t>hora_sin</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.02499809366178784</v>
+        <v>0.06918462109332678</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>meta_std_6</t>
+          <t>temperatura_2m</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.02475794185242257</v>
+        <v>0.04093545937325725</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>hora_decimal</t>
+          <t>cobertura_nuvens</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.0247247249282559</v>
+        <v>0.03763904462044872</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>meta_std_12</t>
+          <t>umidade_relativa</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.02456623391622565</v>
+        <v>0.03575884682007352</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>meta_std_3</t>
+          <t>hora</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.02442628323645508</v>
+        <v>0.02137358307837596</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>meta_delta_4</t>
+          <t>dia_semana</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.02440084174638913</v>
+        <v>0.02008823935692258</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>tendencia_media_meta</t>
+          <t>dia_semana_sin</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.02404829191446472</v>
+        <v>0.01835030511548574</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>meta_std_4</t>
+          <t>dia_semana_cos</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.02356295260645998</v>
+        <v>0.01358143378989688</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>meta_lag_1</t>
+          <t>chuva_mm</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.02354674741781626</v>
+        <v>0.01067391370865662</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>meta_media_12</t>
+          <t>bloco_dia_cod</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.02316646616211172</v>
+        <v>0.008055891383967123</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>meta_delta_2</t>
+          <t>mes_sin</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.02298148156125238</v>
+        <v>0.006857287761682498</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>meta_delta_1</t>
+          <t>mes_cos</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.0229461670378541</v>
+        <v>0.006779041990972015</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>meta_media_6</t>
+          <t>mes</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.02255519446691432</v>
+        <v>0.006749987394773932</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>meta_lag_12</t>
+          <t>eh_sabado</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.02252139603033223</v>
+        <v>0.006273235357722268</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>meta_lag_6</t>
+          <t>estava_chovendo</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.0223717657517269</v>
+        <v>0.005051610245199651</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>meta_lag_3</t>
+          <t>eh_dia_util</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.021999646984066</v>
+        <v>0.004714491596251461</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>meta_lag_4</t>
+          <t>fim_semana</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.02186367163855361</v>
+        <v>0.00448458267553458</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>meta_media_4</t>
+          <t>bloco_tarde_pico</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.0218138693944217</v>
+        <v>0.002812268597845397</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>meta_lag_2</t>
+          <t>bloco_almoco</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.02172453892375165</v>
+        <v>0.00268851334223005</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>meta_media_3</t>
+          <t>eh_domingo</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.02050311973464519</v>
+        <v>0.002662782292511007</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>meta_max_4</t>
+          <t>bloco_noite</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.01708291727492883</v>
+        <v>0.002606415390384498</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>meta_min_4</t>
+          <t>bloco_manha</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.01690810654004981</v>
+        <v>0.002593854543761507</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>temperatura_2m</t>
+          <t>eh_sexta</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.01459161886943071</v>
+        <v>0.002027294424629204</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>meta_max_12</t>
+          <t>eh_pico_tarde</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.01453801004016982</v>
+        <v>0.001996586637448242</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>umidade_relativa</t>
+          <t>eh_pico_manha</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.01423934134647972</v>
+        <v>0.001866573484096053</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>meta_min_12</t>
+          <t>bloco_pico_manha</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.01395689437461835</v>
+        <v>0.001370722578354009</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>cobertura_nuvens</t>
+          <t>bloco_madrugada</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.01355486118270406</v>
+        <v>0.001179673558608982</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>hora_cos</t>
+          <t>bloco_late_night</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.01070397995848734</v>
+        <v>0.0009468129501682338</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>media_alvo_12</t>
+          <t>bloco_outro</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.009847954175694928</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>hora_sin</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>0.009556458120322466</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>soma_alvo_12</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>0.00953520164321066</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>media_alvo_6</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>0.009158001557246012</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>hora</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>0.008967493156039614</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>soma_alvo_6</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>0.008950771590209353</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>tendencia_curta_1_3</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>0.007589558378963959</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>media_alvo_3</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>0.006646368418138178</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>dia_semana</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>0.006601698084716433</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>soma_alvo_3</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>0.006214316178620769</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>tendencia_curta_1_2</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>0.006160373435001119</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>dia_semana_sin</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>0.005957646923354002</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>tendencia_curta_1_6</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>0.005896802425312438</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>chuva_mm</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>0.005334959880748009</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>alvo_lag_12</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>0.004626466450162636</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>dia_semana_cos</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>0.004575122589283248</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>alvo_lag_6</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>0.003901066672268756</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>alvo_lag_2</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>0.003815338575544856</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>bloco_dia_cod</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>0.003744341077911026</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>alvo_lag_3</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>0.003576932686210863</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>alvo_lag_4</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>0.003491570757958481</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>alvo_lag_1</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>0.003381921146181213</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>cluster_regime</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>0.00308250848176318</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>mes_cos</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>0.002265571071373363</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>estava_chovendo</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>0.0021521876435111</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>acelerando_meta</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>0.002128213910961689</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>mes</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>0.002038022000735639</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>mes_sin</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>0.001891086645320808</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>cluster_regime_2</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>0.001863778844441168</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>eh_dia_util</t>
-        </is>
-      </c>
-      <c r="B67" t="n">
-        <v>0.001809738615183021</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>eh_sabado</t>
-        </is>
-      </c>
-      <c r="B68" t="n">
-        <v>0.001660572939034421</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>cluster_regime_0</t>
-        </is>
-      </c>
-      <c r="B69" t="n">
-        <v>0.001581184348319445</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>fim_semana</t>
-        </is>
-      </c>
-      <c r="B70" t="n">
-        <v>0.001414688107477705</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>bloco_tarde_pico</t>
-        </is>
-      </c>
-      <c r="B71" t="n">
-        <v>0.001359699025333156</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>eh_domingo</t>
-        </is>
-      </c>
-      <c r="B72" t="n">
-        <v>0.001215763889050971</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>bloco_almoco</t>
-        </is>
-      </c>
-      <c r="B73" t="n">
-        <v>0.001211827036299257</v>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>eh_pico_tarde</t>
-        </is>
-      </c>
-      <c r="B74" t="n">
-        <v>0.001149105935910304</v>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>bloco_noite</t>
-        </is>
-      </c>
-      <c r="B75" t="n">
-        <v>0.00114625512991465</v>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>cluster_regime_1</t>
-        </is>
-      </c>
-      <c r="B76" t="n">
-        <v>0.001108889246331592</v>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>bloco_manha</t>
-        </is>
-      </c>
-      <c r="B77" t="n">
-        <v>0.0009668261067755214</v>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>eh_pico_manha</t>
-        </is>
-      </c>
-      <c r="B78" t="n">
-        <v>0.0007406714776148555</v>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>cluster_regime_3</t>
-        </is>
-      </c>
-      <c r="B79" t="n">
-        <v>0.0006567539542974511</v>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>bloco_madrugada</t>
-        </is>
-      </c>
-      <c r="B80" t="n">
-        <v>0.0006321329556949328</v>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>bloco_pico_manha</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>0.0006038631114719076</v>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>eh_sexta</t>
-        </is>
-      </c>
-      <c r="B82" t="n">
-        <v>0.0005475627035535416</v>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>bloco_late_night</t>
-        </is>
-      </c>
-      <c r="B83" t="n">
-        <v>0.0004585705921156985</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/Rodovias/modelos_rodovias/floriano_rodrigues_pinheiro_km_26_pindamonhangaba_sp_rf_regimes/importancias.xlsx
+++ b/Rodovias/modelos_rodovias/floriano_rodrigues_pinheiro_km_26_pindamonhangaba_sp_rf_regimes/importancias.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B38"/>
+  <dimension ref="A1:B48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -431,370 +431,470 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>interacao_meta_umidade</t>
+          <t>roll5_ratio_pass_total_meta</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.09180322963693868</v>
+        <v>0.0720933661598103</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>interacao_meta_hora_sin</t>
+          <t>roll3_ratio_pass_total_meta</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.08775957850539987</v>
+        <v>0.06989426326385476</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>interacao_meta_hora_cos</t>
+          <t>lag1_ratio_pass_total_meta</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0857921647217891</v>
+        <v>0.06286968501968118</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>interacao_meta_temperatura</t>
+          <t>interacao_meta_hora_cos</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.08570012242804775</v>
+        <v>0.04732764293182681</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>meta_num</t>
+          <t>interacao_meta_umidade</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08320753511633729</v>
+        <v>0.04461826063281316</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>minuto</t>
+          <t>hora_cos</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.08039249665179352</v>
+        <v>0.04191477105180862</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>hora_cos</t>
+          <t>minuto</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.07527899155719341</v>
+        <v>0.04141242592322551</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>hora_decimal</t>
+          <t>meta_num</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.07076280821991568</v>
+        <v>0.03989801339830471</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>hora_sin</t>
+          <t>interacao_meta_temperatura</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.06918462109332678</v>
+        <v>0.03982693323302707</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>temperatura_2m</t>
+          <t>lag1_pass_total_mercado</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.04093545937325725</v>
+        <v>0.03948841629766054</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>cobertura_nuvens</t>
+          <t>roll10_mean_pass_total_mercado</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.03763904462044872</v>
+        <v>0.03931036447389768</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>umidade_relativa</t>
+          <t>interacao_meta_hora_sin</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.03575884682007352</v>
+        <v>0.03880595621485353</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>hora</t>
+          <t>hora_decimal</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.02137358307837596</v>
+        <v>0.03831814304071121</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>dia_semana</t>
+          <t>lag1_pass_tendencia_5m</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.02008823935692258</v>
+        <v>0.03792104969228498</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>dia_semana_sin</t>
+          <t>hora_sin</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.01835030511548574</v>
+        <v>0.03770994379144062</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>dia_semana_cos</t>
+          <t>roll5_mean_pass_total_mercado</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.01358143378989688</v>
+        <v>0.0369731723151473</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>chuva_mm</t>
+          <t>roll3_mean_pass_total_mercado</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.01067391370865662</v>
+        <v>0.03611817427948655</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>bloco_dia_cod</t>
+          <t>lag1_pass_qtd_ultimos_2min</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.008055891383967123</v>
+        <v>0.03343085609686126</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>mes_sin</t>
+          <t>lag1_pass_media_ultimos_2min</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.006857287761682498</v>
+        <v>0.03276435220199105</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>mes_cos</t>
+          <t>cobertura_nuvens</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.006779041990972015</v>
+        <v>0.02511379906810927</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>mes</t>
+          <t>temperatura_2m</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.006749987394773932</v>
+        <v>0.02420920900241336</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>eh_sabado</t>
+          <t>umidade_relativa</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.006273235357722268</v>
+        <v>0.02263056296481483</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>estava_chovendo</t>
+          <t>hora</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.005051610245199651</v>
+        <v>0.01461425794212239</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>eh_dia_util</t>
+          <t>dia_semana_sin</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.004714491596251461</v>
+        <v>0.01028282932258206</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>fim_semana</t>
+          <t>dia_semana</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.00448458267553458</v>
+        <v>0.01002884424538744</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>bloco_tarde_pico</t>
+          <t>chuva_mm</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.002812268597845397</v>
+        <v>0.008397990312898429</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>bloco_almoco</t>
+          <t>dia_semana_cos</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.00268851334223005</v>
+        <v>0.006991731150013574</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>eh_domingo</t>
+          <t>bloco_dia_cod</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.002662782292511007</v>
+        <v>0.006370704188509691</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>bloco_noite</t>
+          <t>mes</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.002606415390384498</v>
+        <v>0.004309873726278916</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>bloco_manha</t>
+          <t>mes_sin</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.002593854543761507</v>
+        <v>0.004275805041795464</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>eh_sexta</t>
+          <t>mes_cos</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.002027294424629204</v>
+        <v>0.004096257388061157</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>eh_pico_tarde</t>
+          <t>eh_sabado</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.001996586637448242</v>
+        <v>0.003178562540954034</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>eh_pico_manha</t>
+          <t>estava_chovendo</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.001866573484096053</v>
+        <v>0.003117397971655556</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>bloco_pico_manha</t>
+          <t>eh_dia_util</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.001370722578354009</v>
+        <v>0.00283244257838717</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>bloco_madrugada</t>
+          <t>fim_semana</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.001179673558608982</v>
+        <v>0.002583575257062569</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>bloco_late_night</t>
+          <t>bloco_noite</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.0009468129501682338</v>
+        <v>0.002155985002703136</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
+          <t>bloco_almoco</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>0.001894713090068491</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>bloco_tarde_pico</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>0.001890380485030467</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>eh_sexta</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>0.001839281317891715</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>bloco_manha</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>0.0018072451934558</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>eh_pico_tarde</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>0.001556952728869492</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>eh_domingo</t>
+        </is>
+      </c>
+      <c r="B43" t="n">
+        <v>0.001553455924420576</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>eh_pico_manha</t>
+        </is>
+      </c>
+      <c r="B44" t="n">
+        <v>0.001195817345271056</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>bloco_pico_manha</t>
+        </is>
+      </c>
+      <c r="B45" t="n">
+        <v>0.001006050794165304</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>bloco_late_night</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>0.0006944267228849862</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>bloco_madrugada</t>
+        </is>
+      </c>
+      <c r="B47" t="n">
+        <v>0.0006760586755061879</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
           <t>bloco_outro</t>
         </is>
       </c>
-      <c r="B38" t="n">
+      <c r="B48" t="n">
         <v>0</v>
       </c>
     </row>
